--- a/单刷2023B/result2.xlsx
+++ b/单刷2023B/result2.xlsx
@@ -1,74 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>测量船距海域中心点处的距离/海里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖宽度/m</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测线方向夹角/°</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -91,32 +70,206 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,179 +535,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" customWidth="1"/>
+    <col width="8.6640625" customWidth="1" min="1" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>覆盖宽度/m</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>测量船距海域中心点处的距离/海里</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="1">
+      <c r="D2" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>测线方向夹角/°</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J2" s="1">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
+      <c r="C3" s="2" t="n">
+        <v>415.69</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>314.89</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>214.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1">
+      <c r="C4" s="2" t="n">
+        <v>416.12</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>273.42</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>237.75</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>202.08</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>166.4</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1">
+      <c r="C5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>416.55</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
+      <c r="C6" s="2" t="n">
+        <v>416.12</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>451.79</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>487.47</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>523.14</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>558.8200000000001</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>594.49</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>630.16</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>665.84</v>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
+      <c r="C7" s="2" t="n">
+        <v>415.69</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>466.09</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>516.49</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>566.89</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>617.29</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>667.6900000000001</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>718.09</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>768.48</v>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1">
+      <c r="C8" s="2" t="n">
+        <v>416.12</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>451.79</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>487.47</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>523.14</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>558.8200000000001</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>594.49</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>630.16</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>665.84</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1">
+      <c r="C9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>416.55</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="C10" s="2" t="n">
+        <v>416.12</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>273.42</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>237.75</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>202.08</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>166.4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:J1"/>
     <mergeCell ref="A3:A10"/>
-    <mergeCell ref="A1:B2"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>